--- a/AWO(july).xlsx
+++ b/AWO(july).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10332"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10044"/>
   </bookViews>
   <sheets>
     <sheet name="AWO(july)" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="39">
   <si>
     <t>ID</t>
   </si>
@@ -42,36 +42,24 @@
     <t>LOAN</t>
   </si>
   <si>
-    <t>OPENING_DATE</t>
+    <t>punishment</t>
   </si>
   <si>
     <t>PHONE_NUM</t>
   </si>
   <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>punishment</t>
-  </si>
-  <si>
     <t>Addunnaa</t>
   </si>
   <si>
     <t>Nuurgii</t>
   </si>
   <si>
-    <t>aduna64@gmail.com</t>
-  </si>
-  <si>
     <t>Baay`isaa</t>
   </si>
   <si>
     <t>Kabbadaa</t>
   </si>
   <si>
-    <t>aayanasa93@gmail.com</t>
-  </si>
-  <si>
     <t>Biraanuu</t>
   </si>
   <si>
@@ -105,9 +93,6 @@
     <t>Diroo</t>
   </si>
   <si>
-    <t>lamidiro22@gmail.com</t>
-  </si>
-  <si>
     <t>Qananiisaa</t>
   </si>
   <si>
@@ -141,9 +126,6 @@
     <t>Walfaanaa</t>
   </si>
   <si>
-    <t>walfanamegersa3@gmail.com</t>
-  </si>
-  <si>
     <t>Xurunaa</t>
   </si>
   <si>
@@ -154,9 +136,6 @@
   </si>
   <si>
     <t>Fayera</t>
-  </si>
-  <si>
-    <t>debere64@example.com</t>
   </si>
 </sst>
 </file>
@@ -640,9 +619,8 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -964,16 +942,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="26.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1001,25 +977,19 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>101</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D2">
-        <v>24900</v>
+        <v>26900</v>
       </c>
       <c r="E2">
         <v>15000</v>
@@ -1030,34 +1000,28 @@
       <c r="G2">
         <v>0</v>
       </c>
-      <c r="H2" s="1">
-        <v>40797</v>
+      <c r="H2">
+        <v>0</v>
       </c>
       <c r="I2">
         <v>913942964</v>
       </c>
-      <c r="J2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D3">
-        <v>24900</v>
+        <v>26900</v>
       </c>
       <c r="E3">
-        <v>11500</v>
+        <v>12375</v>
       </c>
       <c r="F3">
         <v>1000</v>
@@ -1065,31 +1029,25 @@
       <c r="G3">
         <v>0</v>
       </c>
-      <c r="H3" s="1">
-        <v>40797</v>
+      <c r="H3">
+        <v>4125</v>
       </c>
       <c r="I3">
         <v>922948389</v>
       </c>
-      <c r="J3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K3">
-        <v>4125</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D4">
-        <v>24900</v>
+        <v>26900</v>
       </c>
       <c r="E4">
         <v>15500</v>
@@ -1100,31 +1058,25 @@
       <c r="G4">
         <v>0</v>
       </c>
-      <c r="H4" s="1">
-        <v>40797</v>
+      <c r="H4">
+        <v>0</v>
       </c>
       <c r="I4">
         <v>910045632</v>
       </c>
-      <c r="J4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>104</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D5">
-        <v>24900</v>
+        <v>26900</v>
       </c>
       <c r="E5">
         <v>15000</v>
@@ -1135,31 +1087,25 @@
       <c r="G5">
         <v>0</v>
       </c>
-      <c r="H5" s="1">
-        <v>40797</v>
+      <c r="H5">
+        <v>1050</v>
       </c>
       <c r="I5">
         <v>910452943</v>
       </c>
-      <c r="J5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K5">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>105</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D6">
-        <v>24900</v>
+        <v>26900</v>
       </c>
       <c r="E6">
         <v>15000</v>
@@ -1170,31 +1116,25 @@
       <c r="G6">
         <v>0</v>
       </c>
-      <c r="H6" s="1">
-        <v>40797</v>
+      <c r="H6">
+        <v>0</v>
       </c>
       <c r="I6">
         <v>911853155</v>
       </c>
-      <c r="J6" t="s">
-        <v>16</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>106</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>25030</v>
+        <v>26030</v>
       </c>
       <c r="E7">
         <v>15000</v>
@@ -1205,31 +1145,25 @@
       <c r="G7">
         <v>10000</v>
       </c>
-      <c r="H7" s="1">
-        <v>40797</v>
+      <c r="H7">
+        <v>1198.5</v>
       </c>
       <c r="I7">
         <v>925382373</v>
       </c>
-      <c r="J7" t="s">
-        <v>16</v>
-      </c>
-      <c r="K7">
-        <v>1048.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>107</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D8">
-        <v>24900</v>
+        <v>26900</v>
       </c>
       <c r="E8">
         <v>15000</v>
@@ -1240,31 +1174,25 @@
       <c r="G8">
         <v>0</v>
       </c>
-      <c r="H8" s="1">
-        <v>40797</v>
+      <c r="H8">
+        <v>300</v>
       </c>
       <c r="I8">
         <v>954846351</v>
       </c>
-      <c r="J8" t="s">
-        <v>16</v>
-      </c>
-      <c r="K8">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>108</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D9">
-        <v>24900</v>
+        <v>26900</v>
       </c>
       <c r="E9">
         <v>15000</v>
@@ -1275,31 +1203,25 @@
       <c r="G9">
         <v>0</v>
       </c>
-      <c r="H9" s="1">
-        <v>40797</v>
+      <c r="H9">
+        <v>600</v>
       </c>
       <c r="I9">
         <v>922956646</v>
       </c>
-      <c r="J9" t="s">
-        <v>28</v>
-      </c>
-      <c r="K9">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>109</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D10">
-        <v>25000</v>
+        <v>27000</v>
       </c>
       <c r="E10">
         <v>15000</v>
@@ -1310,31 +1232,25 @@
       <c r="G10">
         <v>0</v>
       </c>
-      <c r="H10" s="1">
-        <v>40797</v>
+      <c r="H10">
+        <v>0</v>
       </c>
       <c r="I10">
         <v>921761067</v>
       </c>
-      <c r="J10" t="s">
-        <v>16</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1010</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D11">
-        <v>24900</v>
+        <v>26900</v>
       </c>
       <c r="E11">
         <v>15000</v>
@@ -1345,31 +1261,25 @@
       <c r="G11">
         <v>0</v>
       </c>
-      <c r="H11" s="1">
-        <v>40797</v>
+      <c r="H11">
+        <v>900</v>
       </c>
       <c r="I11">
         <v>913235855</v>
       </c>
-      <c r="J11" t="s">
-        <v>16</v>
-      </c>
-      <c r="K11">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1011</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D12">
-        <v>24900</v>
+        <v>26900</v>
       </c>
       <c r="E12">
         <v>15000</v>
@@ -1380,31 +1290,25 @@
       <c r="G12">
         <v>0</v>
       </c>
-      <c r="H12" s="1">
-        <v>40797</v>
+      <c r="H12">
+        <v>750</v>
       </c>
       <c r="I12">
         <v>985816078</v>
       </c>
-      <c r="J12" t="s">
-        <v>16</v>
-      </c>
-      <c r="K12">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1012</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D13">
-        <v>24900</v>
+        <v>26900</v>
       </c>
       <c r="E13">
         <v>15000</v>
@@ -1415,31 +1319,25 @@
       <c r="G13">
         <v>0</v>
       </c>
-      <c r="H13" s="1">
-        <v>40797</v>
+      <c r="H13">
+        <v>0</v>
       </c>
       <c r="I13">
         <v>913952050</v>
       </c>
-      <c r="J13" t="s">
-        <v>16</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1013</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D14">
-        <v>24400</v>
+        <v>26900</v>
       </c>
       <c r="E14">
         <v>15000</v>
@@ -1450,31 +1348,25 @@
       <c r="G14">
         <v>0</v>
       </c>
-      <c r="H14" s="1">
-        <v>40797</v>
+      <c r="H14">
+        <v>300</v>
       </c>
       <c r="I14">
         <v>923605989</v>
       </c>
-      <c r="J14" t="s">
-        <v>16</v>
-      </c>
-      <c r="K14">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1014</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D15">
-        <v>24900</v>
+        <v>26900</v>
       </c>
       <c r="E15">
         <v>15000</v>
@@ -1485,66 +1377,54 @@
       <c r="G15">
         <v>0</v>
       </c>
-      <c r="H15" s="1">
-        <v>40797</v>
+      <c r="H15">
+        <v>0</v>
       </c>
       <c r="I15">
         <v>912659004</v>
       </c>
-      <c r="J15" t="s">
-        <v>16</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1015</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D16">
-        <v>24900</v>
+        <v>26900</v>
       </c>
       <c r="E16">
         <v>15000</v>
       </c>
       <c r="F16">
-        <v>284000</v>
+        <v>285950</v>
       </c>
       <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16" s="1">
-        <v>40797</v>
+        <v>10000</v>
+      </c>
+      <c r="H16">
+        <v>3000</v>
       </c>
       <c r="I16">
         <v>912861288</v>
       </c>
-      <c r="J16" t="s">
-        <v>40</v>
-      </c>
-      <c r="K16">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1016</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D17">
-        <v>24900</v>
+        <v>26900</v>
       </c>
       <c r="E17">
         <v>15000</v>
@@ -1555,28 +1435,22 @@
       <c r="G17">
         <v>0</v>
       </c>
-      <c r="H17" s="1">
-        <v>40797</v>
+      <c r="H17">
+        <v>3900</v>
       </c>
       <c r="I17">
         <v>948594041</v>
       </c>
-      <c r="J17" t="s">
-        <v>40</v>
-      </c>
-      <c r="K17">
-        <v>3900</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1017</v>
       </c>
       <c r="B18" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D18">
         <v>11000</v>
@@ -1590,17 +1464,11 @@
       <c r="G18">
         <v>0</v>
       </c>
-      <c r="H18" s="1">
-        <v>45895</v>
+      <c r="H18">
+        <v>933.5</v>
       </c>
       <c r="I18">
         <v>912214364</v>
-      </c>
-      <c r="J18" t="s">
-        <v>45</v>
-      </c>
-      <c r="K18">
-        <v>495</v>
       </c>
     </row>
   </sheetData>

--- a/AWO(july).xlsx
+++ b/AWO(july).xlsx
@@ -945,7 +945,6 @@
   <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="8" max="8" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1372,7 +1371,7 @@
         <v>15000</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="G15">
         <v>0</v>

--- a/AWO(july).xlsx
+++ b/AWO(july).xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\walfaanaam\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\walfaanaam\Desktop\general\AWO\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -619,8 +619,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -945,7 +946,7 @@
   <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="9" max="9" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.21875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -973,7 +974,7 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
@@ -988,7 +989,7 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>26900</v>
+        <v>27900</v>
       </c>
       <c r="E2">
         <v>15000</v>
@@ -1002,7 +1003,7 @@
       <c r="H2">
         <v>0</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="1">
         <v>913942964</v>
       </c>
     </row>
@@ -1017,7 +1018,7 @@
         <v>12</v>
       </c>
       <c r="D3">
-        <v>26900</v>
+        <v>28400</v>
       </c>
       <c r="E3">
         <v>12375</v>
@@ -1031,7 +1032,7 @@
       <c r="H3">
         <v>4125</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>922948389</v>
       </c>
     </row>
@@ -1046,7 +1047,7 @@
         <v>14</v>
       </c>
       <c r="D4">
-        <v>26900</v>
+        <v>28400</v>
       </c>
       <c r="E4">
         <v>15500</v>
@@ -1060,7 +1061,7 @@
       <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>910045632</v>
       </c>
     </row>
@@ -1075,7 +1076,7 @@
         <v>16</v>
       </c>
       <c r="D5">
-        <v>26900</v>
+        <v>28400</v>
       </c>
       <c r="E5">
         <v>15000</v>
@@ -1089,7 +1090,7 @@
       <c r="H5">
         <v>1050</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="1">
         <v>910452943</v>
       </c>
     </row>
@@ -1104,7 +1105,7 @@
         <v>16</v>
       </c>
       <c r="D6">
-        <v>26900</v>
+        <v>28400</v>
       </c>
       <c r="E6">
         <v>15000</v>
@@ -1118,7 +1119,7 @@
       <c r="H6">
         <v>0</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="1">
         <v>911853155</v>
       </c>
     </row>
@@ -1133,7 +1134,7 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>26030</v>
+        <v>26530</v>
       </c>
       <c r="E7">
         <v>15000</v>
@@ -1147,7 +1148,7 @@
       <c r="H7">
         <v>1198.5</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="1">
         <v>925382373</v>
       </c>
     </row>
@@ -1162,7 +1163,7 @@
         <v>21</v>
       </c>
       <c r="D8">
-        <v>26900</v>
+        <v>28400</v>
       </c>
       <c r="E8">
         <v>15000</v>
@@ -1176,7 +1177,7 @@
       <c r="H8">
         <v>300</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="1">
         <v>954846351</v>
       </c>
     </row>
@@ -1191,7 +1192,7 @@
         <v>23</v>
       </c>
       <c r="D9">
-        <v>26900</v>
+        <v>28400</v>
       </c>
       <c r="E9">
         <v>15000</v>
@@ -1205,7 +1206,7 @@
       <c r="H9">
         <v>600</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="1">
         <v>922956646</v>
       </c>
     </row>
@@ -1220,7 +1221,7 @@
         <v>25</v>
       </c>
       <c r="D10">
-        <v>27000</v>
+        <v>28500</v>
       </c>
       <c r="E10">
         <v>15000</v>
@@ -1234,7 +1235,7 @@
       <c r="H10">
         <v>0</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="1">
         <v>921761067</v>
       </c>
     </row>
@@ -1263,7 +1264,7 @@
       <c r="H11">
         <v>900</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="1">
         <v>913235855</v>
       </c>
     </row>
@@ -1278,7 +1279,7 @@
         <v>19</v>
       </c>
       <c r="D12">
-        <v>26900</v>
+        <v>27900</v>
       </c>
       <c r="E12">
         <v>15000</v>
@@ -1292,7 +1293,7 @@
       <c r="H12">
         <v>750</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="1">
         <v>985816078</v>
       </c>
     </row>
@@ -1307,7 +1308,7 @@
         <v>30</v>
       </c>
       <c r="D13">
-        <v>26900</v>
+        <v>28400</v>
       </c>
       <c r="E13">
         <v>15000</v>
@@ -1321,7 +1322,7 @@
       <c r="H13">
         <v>0</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="1">
         <v>913952050</v>
       </c>
     </row>
@@ -1336,7 +1337,7 @@
         <v>31</v>
       </c>
       <c r="D14">
-        <v>26900</v>
+        <v>27900</v>
       </c>
       <c r="E14">
         <v>15000</v>
@@ -1350,7 +1351,7 @@
       <c r="H14">
         <v>300</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="1">
         <v>923605989</v>
       </c>
     </row>
@@ -1365,7 +1366,7 @@
         <v>33</v>
       </c>
       <c r="D15">
-        <v>26900</v>
+        <v>27900</v>
       </c>
       <c r="E15">
         <v>15000</v>
@@ -1379,7 +1380,7 @@
       <c r="H15">
         <v>0</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="1">
         <v>912659004</v>
       </c>
     </row>
@@ -1394,7 +1395,7 @@
         <v>21</v>
       </c>
       <c r="D16">
-        <v>26900</v>
+        <v>28400</v>
       </c>
       <c r="E16">
         <v>15000</v>
@@ -1408,7 +1409,7 @@
       <c r="H16">
         <v>3000</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="1">
         <v>912861288</v>
       </c>
     </row>
@@ -1423,7 +1424,7 @@
         <v>36</v>
       </c>
       <c r="D17">
-        <v>26900</v>
+        <v>28400</v>
       </c>
       <c r="E17">
         <v>15000</v>
@@ -1437,7 +1438,7 @@
       <c r="H17">
         <v>3900</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="1">
         <v>948594041</v>
       </c>
     </row>
@@ -1466,11 +1467,12 @@
       <c r="H18">
         <v>933.5</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="1">
         <v>912214364</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/AWO(july).xlsx
+++ b/AWO(july).xlsx
@@ -619,9 +619,8 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -946,7 +945,7 @@
   <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="9" max="9" width="12.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -974,7 +973,7 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1003,7 +1002,7 @@
       <c r="H2">
         <v>0</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2">
         <v>913942964</v>
       </c>
     </row>
@@ -1032,7 +1031,7 @@
       <c r="H3">
         <v>4125</v>
       </c>
-      <c r="I3" s="1">
+      <c r="I3">
         <v>922948389</v>
       </c>
     </row>
@@ -1061,7 +1060,7 @@
       <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4" s="1">
+      <c r="I4">
         <v>910045632</v>
       </c>
     </row>
@@ -1082,7 +1081,7 @@
         <v>15000</v>
       </c>
       <c r="F5">
-        <v>17000</v>
+        <v>27000</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1090,7 +1089,7 @@
       <c r="H5">
         <v>1050</v>
       </c>
-      <c r="I5" s="1">
+      <c r="I5">
         <v>910452943</v>
       </c>
     </row>
@@ -1119,7 +1118,7 @@
       <c r="H6">
         <v>0</v>
       </c>
-      <c r="I6" s="1">
+      <c r="I6">
         <v>911853155</v>
       </c>
     </row>
@@ -1148,7 +1147,7 @@
       <c r="H7">
         <v>1198.5</v>
       </c>
-      <c r="I7" s="1">
+      <c r="I7">
         <v>925382373</v>
       </c>
     </row>
@@ -1177,7 +1176,7 @@
       <c r="H8">
         <v>300</v>
       </c>
-      <c r="I8" s="1">
+      <c r="I8">
         <v>954846351</v>
       </c>
     </row>
@@ -1206,7 +1205,7 @@
       <c r="H9">
         <v>600</v>
       </c>
-      <c r="I9" s="1">
+      <c r="I9">
         <v>922956646</v>
       </c>
     </row>
@@ -1235,7 +1234,7 @@
       <c r="H10">
         <v>0</v>
       </c>
-      <c r="I10" s="1">
+      <c r="I10">
         <v>921761067</v>
       </c>
     </row>
@@ -1264,7 +1263,7 @@
       <c r="H11">
         <v>900</v>
       </c>
-      <c r="I11" s="1">
+      <c r="I11">
         <v>913235855</v>
       </c>
     </row>
@@ -1293,7 +1292,7 @@
       <c r="H12">
         <v>750</v>
       </c>
-      <c r="I12" s="1">
+      <c r="I12">
         <v>985816078</v>
       </c>
     </row>
@@ -1322,7 +1321,7 @@
       <c r="H13">
         <v>0</v>
       </c>
-      <c r="I13" s="1">
+      <c r="I13">
         <v>913952050</v>
       </c>
     </row>
@@ -1351,7 +1350,7 @@
       <c r="H14">
         <v>300</v>
       </c>
-      <c r="I14" s="1">
+      <c r="I14">
         <v>923605989</v>
       </c>
     </row>
@@ -1380,7 +1379,7 @@
       <c r="H15">
         <v>0</v>
       </c>
-      <c r="I15" s="1">
+      <c r="I15">
         <v>912659004</v>
       </c>
     </row>
@@ -1401,7 +1400,7 @@
         <v>15000</v>
       </c>
       <c r="F16">
-        <v>285950</v>
+        <v>295950</v>
       </c>
       <c r="G16">
         <v>10000</v>
@@ -1409,7 +1408,7 @@
       <c r="H16">
         <v>3000</v>
       </c>
-      <c r="I16" s="1">
+      <c r="I16">
         <v>912861288</v>
       </c>
     </row>
@@ -1438,7 +1437,7 @@
       <c r="H17">
         <v>3900</v>
       </c>
-      <c r="I17" s="1">
+      <c r="I17">
         <v>948594041</v>
       </c>
     </row>
@@ -1467,12 +1466,11 @@
       <c r="H18">
         <v>933.5</v>
       </c>
-      <c r="I18" s="1">
+      <c r="I18">
         <v>912214364</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/AWO(july).xlsx
+++ b/AWO(july).xlsx
@@ -945,6 +945,13 @@
   <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -988,7 +995,7 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>27900</v>
+        <v>28400</v>
       </c>
       <c r="E2">
         <v>15000</v>
@@ -1020,7 +1027,7 @@
         <v>28400</v>
       </c>
       <c r="E3">
-        <v>12375</v>
+        <v>15000</v>
       </c>
       <c r="F3">
         <v>1000</v>
@@ -1049,7 +1056,7 @@
         <v>28400</v>
       </c>
       <c r="E4">
-        <v>15500</v>
+        <v>15000</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -1142,7 +1149,7 @@
         <v>13500</v>
       </c>
       <c r="G7">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="H7">
         <v>1198.5</v>
@@ -1249,7 +1256,7 @@
         <v>27</v>
       </c>
       <c r="D11">
-        <v>26900</v>
+        <v>27400</v>
       </c>
       <c r="E11">
         <v>15000</v>
@@ -1278,7 +1285,7 @@
         <v>19</v>
       </c>
       <c r="D12">
-        <v>27900</v>
+        <v>28400</v>
       </c>
       <c r="E12">
         <v>15000</v>
@@ -1287,7 +1294,7 @@
         <v>10000</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="H12">
         <v>750</v>
@@ -1472,5 +1479,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/AWO(july).xlsx
+++ b/AWO(july).xlsx
@@ -945,13 +945,7 @@
   <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1256,7 +1250,7 @@
         <v>27</v>
       </c>
       <c r="D11">
-        <v>27400</v>
+        <v>27900</v>
       </c>
       <c r="E11">
         <v>15000</v>
@@ -1479,6 +1473,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>